--- a/testdata/AddEmployee.xlsx
+++ b/testdata/AddEmployee.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="9495" windowHeight="1575"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="12240" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>FristName</t>
   </si>
@@ -39,22 +40,19 @@
     <t>confirmpassword</t>
   </si>
   <si>
-    <t>Gireesh</t>
-  </si>
-  <si>
     <t>Settli</t>
   </si>
   <si>
-    <t>Nataraja</t>
-  </si>
-  <si>
-    <t>CFSI897</t>
-  </si>
-  <si>
     <t>Gireesha</t>
   </si>
   <si>
-    <t>Giri@123</t>
+    <t>Medha@123</t>
+  </si>
+  <si>
+    <t>Medha1</t>
+  </si>
+  <si>
+    <t>Medha9</t>
   </si>
 </sst>
 </file>
@@ -435,25 +433,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
